--- a/main/01原始资料/第一卷(500)修改(2).xlsx
+++ b/main/01原始资料/第一卷(500)修改(2).xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1160" uniqueCount="1107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1161" uniqueCount="1108">
   <si>
     <t>原文页码</t>
   </si>
@@ -53,6 +53,9 @@
   </si>
   <si>
     <t>备注</t>
+  </si>
+  <si>
+    <t>分类</t>
   </si>
   <si>
     <t>5-1</t>
@@ -15102,6 +15105,7 @@
     <col min="5" max="5" width="28.4907407407407" customWidth="1"/>
     <col min="6" max="6" width="32.6666666666667" style="7" customWidth="1"/>
     <col min="7" max="7" width="13.4907407407407" customWidth="1"/>
+    <col min="8" max="8" width="13.8055555555556" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="30.6" spans="1:18">
@@ -15126,33 +15130,36 @@
       <c r="G1" s="12" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="12" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="213.6" spans="1:18">
       <c r="A2" s="13">
         <v>1</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" s="16"/>
     </row>
     <row r="3" s="2" customFormat="1" ht="31.2" spans="1:18">
       <c r="A3" s="13"/>
       <c r="B3" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3" s="16"/>
       <c r="E3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
@@ -15170,17 +15177,17 @@
     <row r="4" s="2" customFormat="1" ht="31.2" spans="1:18">
       <c r="A4" s="13"/>
       <c r="B4" s="14" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D4" s="16"/>
       <c r="E4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
@@ -15198,17 +15205,17 @@
     <row r="5" s="2" customFormat="1" ht="31.2" spans="1:18">
       <c r="A5" s="13"/>
       <c r="B5" s="14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D5" s="16"/>
       <c r="E5" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
@@ -15226,17 +15233,17 @@
     <row r="6" s="2" customFormat="1" ht="43.2" spans="1:18">
       <c r="A6" s="13"/>
       <c r="B6" s="14" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D6" s="16"/>
       <c r="E6" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F6" s="16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
@@ -15254,17 +15261,17 @@
     <row r="7" s="2" customFormat="1" ht="409.5" spans="1:18">
       <c r="A7" s="13"/>
       <c r="B7" s="14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D7" s="16"/>
       <c r="E7" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F7" s="16" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
@@ -15284,17 +15291,17 @@
         <v>10</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D8" s="16"/>
       <c r="E8" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F8" s="16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
@@ -15312,46 +15319,46 @@
     <row r="9" s="1" customFormat="1" ht="28.8" spans="1:18">
       <c r="A9" s="19"/>
       <c r="B9" s="14" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D9" s="16"/>
       <c r="E9" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="28.8" spans="1:18">
       <c r="A10" s="19"/>
       <c r="B10" s="14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D10" s="16"/>
       <c r="E10" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="25.8" spans="1:18">
       <c r="A11" s="19"/>
       <c r="B11" s="14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D11" s="16"/>
       <c r="E11" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="25.8" spans="1:18">
@@ -15359,85 +15366,85 @@
         <v>11</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C12" s="21" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D12" s="16"/>
       <c r="E12" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="25.8" spans="1:18">
       <c r="A13" s="19"/>
       <c r="B13" s="14" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C13" s="22" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D13" s="16"/>
       <c r="E13" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="28.8" spans="1:18">
       <c r="A14" s="19"/>
       <c r="B14" s="14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C14" s="22" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D14" s="16"/>
       <c r="E14" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" ht="25.8" spans="1:18">
       <c r="A15" s="19"/>
       <c r="B15" s="14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C15" s="22" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D15" s="16"/>
       <c r="E15" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" ht="28.8" spans="1:18">
       <c r="A16" s="19"/>
       <c r="B16" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C16" s="22" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D16" s="16"/>
       <c r="E16" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" ht="25.8" spans="1:6">
       <c r="A17" s="19"/>
       <c r="B17" s="14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D17" s="16"/>
       <c r="E17" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="28.8" spans="1:6">
@@ -15445,17 +15452,17 @@
         <v>12</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D18" s="16"/>
       <c r="E18" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" ht="72" spans="1:6">
@@ -15463,58 +15470,58 @@
         <v>12</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D19" s="16"/>
       <c r="E19" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20" s="3" customFormat="1" ht="187.2" spans="1:6">
       <c r="A20" s="23"/>
       <c r="B20" s="24" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C20" s="25" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D20" s="26"/>
       <c r="E20" s="27" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F20" s="26" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="21" s="3" customFormat="1" ht="25.8" spans="1:6">
       <c r="A21" s="23"/>
       <c r="B21" s="24" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C21" s="25" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D21" s="26"/>
       <c r="E21" s="27" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="22" s="3" customFormat="1" ht="25.8" spans="1:6">
       <c r="A22" s="23"/>
       <c r="B22" s="24" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C22" s="25" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D22" s="26"/>
       <c r="E22" s="27"/>
@@ -15522,15 +15529,15 @@
     <row r="23" s="3" customFormat="1" ht="409.5" spans="1:6">
       <c r="A23" s="23"/>
       <c r="B23" s="24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C23" s="25" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D23" s="26"/>
       <c r="E23" s="27"/>
       <c r="F23" s="26" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="24" s="3" customFormat="1" ht="51.6" spans="1:6">
@@ -15538,14 +15545,14 @@
         <v>13</v>
       </c>
       <c r="B24" s="24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C24" s="25" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D24" s="26"/>
       <c r="E24" s="27" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25" s="3" customFormat="1" ht="172.8" spans="1:6">
@@ -15553,120 +15560,120 @@
         <v>14</v>
       </c>
       <c r="B25" s="24" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C25" s="28" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D25" s="26"/>
       <c r="E25" s="27" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F25" s="26" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" ht="25.8" spans="1:6">
       <c r="A26" s="19"/>
       <c r="B26" s="14" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D26" s="16"/>
       <c r="E26" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" ht="25.8" spans="1:6">
       <c r="A27" s="19"/>
       <c r="B27" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D27" s="16"/>
       <c r="E27" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" ht="25.8" spans="1:6">
       <c r="A28" s="19"/>
       <c r="B28" s="14" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D28" s="16"/>
       <c r="E28" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" ht="25.8" spans="1:6">
       <c r="A29" s="19"/>
       <c r="B29" s="14" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C29" s="21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D29" s="16"/>
       <c r="E29" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" ht="25.8" spans="1:6">
       <c r="A30" s="19"/>
       <c r="B30" s="14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C30" s="21" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D30" s="16"/>
       <c r="E30" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" ht="28.8" spans="1:6">
       <c r="A31" s="19"/>
       <c r="B31" s="14" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C31" s="20" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D31" s="16"/>
       <c r="E31" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" ht="25.8" spans="1:6">
       <c r="A32" s="19"/>
       <c r="B32" s="14" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C32" s="21" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D32" s="16"/>
       <c r="E32" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" ht="28.8" spans="1:7">
@@ -15674,46 +15681,46 @@
         <v>15</v>
       </c>
       <c r="B33" s="14" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C33" s="20" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D33" s="16"/>
       <c r="E33" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" ht="25.8" spans="1:7">
       <c r="A34" s="19"/>
       <c r="B34" s="14" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C34" s="21" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D34" s="16"/>
       <c r="E34" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" ht="28.8" spans="1:7">
       <c r="A35" s="19"/>
       <c r="B35" s="14" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C35" s="20" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D35" s="16"/>
       <c r="E35" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="1" ht="409.5" spans="1:7">
@@ -15721,17 +15728,17 @@
         <v>15</v>
       </c>
       <c r="B36" s="14" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C36" s="21" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D36" s="16"/>
       <c r="E36" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F36" s="16" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="37" s="1" customFormat="1" ht="25.8" spans="1:7">
@@ -15739,14 +15746,14 @@
         <v>16</v>
       </c>
       <c r="B37" s="14" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C37" s="29" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D37" s="16"/>
       <c r="E37" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="38" s="1" customFormat="1" ht="302.4" spans="1:7">
@@ -15754,31 +15761,31 @@
         <v>17</v>
       </c>
       <c r="B38" s="14" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C38" s="20" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D38" s="16"/>
       <c r="E38" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F38" s="1"/>
       <c r="G38" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="39" s="1" customFormat="1" ht="25.8" spans="1:7">
       <c r="A39" s="19"/>
       <c r="B39" s="14" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C39" s="20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D39" s="16"/>
       <c r="E39" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="40" s="1" customFormat="1" ht="273.6" spans="1:7">
@@ -15786,17 +15793,17 @@
         <v>18</v>
       </c>
       <c r="B40" s="14" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C40" s="20" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D40" s="16"/>
       <c r="E40" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F40" s="16" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="41" s="3" customFormat="1" ht="388.8" spans="1:7">
@@ -15804,17 +15811,17 @@
         <v>19</v>
       </c>
       <c r="B41" s="24" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C41" s="28" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D41" s="26"/>
       <c r="E41" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F41" s="26" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="42" s="3" customFormat="1" ht="158.4" spans="1:7">
@@ -15822,17 +15829,17 @@
         <v>19</v>
       </c>
       <c r="B42" s="24" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C42" s="28" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D42" s="26"/>
       <c r="E42" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F42" s="26" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="43" s="1" customFormat="1" ht="28.8" spans="1:7">
@@ -15840,17 +15847,17 @@
         <v>20</v>
       </c>
       <c r="B43" s="14" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C43" s="20" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D43" s="16"/>
       <c r="E43" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F43" s="16" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="44" s="1" customFormat="1" ht="409.5" spans="1:7">
@@ -15858,17 +15865,17 @@
         <v>20</v>
       </c>
       <c r="B44" s="14" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C44" s="21" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D44" s="16"/>
       <c r="E44" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F44" s="16" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="45" s="1" customFormat="1" ht="86.4" spans="1:7">
@@ -15876,17 +15883,17 @@
         <v>21</v>
       </c>
       <c r="B45" s="14" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C45" s="20" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D45" s="16"/>
       <c r="E45" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F45" s="16" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="46" s="1" customFormat="1" ht="43.2" spans="1:7">
@@ -15894,17 +15901,17 @@
         <v>21</v>
       </c>
       <c r="B46" s="14" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C46" s="20" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D46" s="16"/>
       <c r="E46" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="47" s="1" customFormat="1" ht="172.8" spans="1:7">
@@ -15912,33 +15919,33 @@
         <v>21</v>
       </c>
       <c r="B47" s="14" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C47" s="20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D47" s="16"/>
       <c r="E47" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F47" s="16" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="48" s="4" customFormat="1" ht="25.8" spans="1:7">
       <c r="A48" s="30"/>
       <c r="B48" s="31" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C48" s="32" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D48" s="33"/>
       <c r="E48" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="49" s="4" customFormat="1" ht="172.8" spans="1:18">
@@ -15946,30 +15953,30 @@
         <v>22</v>
       </c>
       <c r="B49" s="31" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C49" s="32" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D49" s="33"/>
       <c r="E49" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F49" s="33" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="50" s="4" customFormat="1" ht="28.8" spans="1:18">
       <c r="A50" s="30"/>
       <c r="B50" s="31" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C50" s="34" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D50" s="33"/>
       <c r="E50" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F50" s="33"/>
     </row>
@@ -15978,30 +15985,30 @@
         <v>22</v>
       </c>
       <c r="B51" s="31" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C51" s="34" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D51" s="33"/>
       <c r="E51" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F51" s="33" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="52" s="1" customFormat="1" ht="25.8" spans="1:18">
       <c r="A52" s="19"/>
       <c r="B52" s="14" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C52" s="21" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D52" s="16"/>
       <c r="E52" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="53" s="1" customFormat="1" ht="25.8" spans="1:18">
@@ -16009,10 +16016,10 @@
         <v>23</v>
       </c>
       <c r="B53" s="14" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C53" s="21" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D53" s="16"/>
     </row>
@@ -16021,10 +16028,10 @@
         <v>23</v>
       </c>
       <c r="B54" s="14" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C54" s="20" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D54" s="16"/>
     </row>
@@ -16033,10 +16040,10 @@
         <v>23</v>
       </c>
       <c r="B55" s="14" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C55" s="21" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D55" s="16"/>
     </row>
@@ -16045,10 +16052,10 @@
         <v>24</v>
       </c>
       <c r="B56" s="31" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C56" s="32" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D56" s="33"/>
     </row>
@@ -16057,10 +16064,10 @@
         <v>24</v>
       </c>
       <c r="B57" s="14" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C57" s="20" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D57" s="16"/>
     </row>
@@ -16069,10 +16076,10 @@
         <v>24</v>
       </c>
       <c r="B58" s="31" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C58" s="35" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D58" s="33"/>
     </row>
@@ -16081,10 +16088,10 @@
         <v>25</v>
       </c>
       <c r="B59" s="14" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C59" s="20" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D59" s="16"/>
       <c r="E59" s="1"/>
@@ -16107,10 +16114,10 @@
         <v>26</v>
       </c>
       <c r="B60" s="31" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C60" s="32" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D60" s="33"/>
     </row>
@@ -16119,10 +16126,10 @@
         <v>26</v>
       </c>
       <c r="B61" s="31" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C61" s="34" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D61" s="33"/>
     </row>
@@ -16131,10 +16138,10 @@
         <v>26</v>
       </c>
       <c r="B62" s="14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C62" s="20" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D62" s="16"/>
     </row>
@@ -16143,10 +16150,10 @@
         <v>27</v>
       </c>
       <c r="B63" s="14" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C63" s="21" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D63" s="16"/>
     </row>
@@ -16155,10 +16162,10 @@
         <v>29</v>
       </c>
       <c r="B64" s="14" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C64" s="20" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D64" s="16"/>
     </row>
@@ -16167,10 +16174,10 @@
         <v>30</v>
       </c>
       <c r="B65" s="14" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C65" s="21" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D65" s="16"/>
     </row>
@@ -16179,10 +16186,10 @@
         <v>31</v>
       </c>
       <c r="B66" s="14" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C66" s="20" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D66" s="16"/>
     </row>
@@ -16191,10 +16198,10 @@
         <v>31</v>
       </c>
       <c r="B67" s="14" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C67" s="21" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D67" s="16"/>
       <c r="E67" s="1"/>
@@ -16217,10 +16224,10 @@
         <v>31</v>
       </c>
       <c r="B68" s="14" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C68" s="21" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D68" s="16"/>
       <c r="E68" s="1"/>
@@ -16243,10 +16250,10 @@
         <v>31</v>
       </c>
       <c r="B69" s="14" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C69" s="21" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D69" s="16"/>
     </row>
@@ -16255,10 +16262,10 @@
         <v>32</v>
       </c>
       <c r="B70" s="14" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C70" s="21" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D70" s="16"/>
       <c r="E70" s="1"/>
@@ -16281,10 +16288,10 @@
         <v>32</v>
       </c>
       <c r="B71" s="14" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C71" s="21" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D71" s="16"/>
     </row>
@@ -16293,10 +16300,10 @@
         <v>33</v>
       </c>
       <c r="B72" s="14" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C72" s="21" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D72" s="16"/>
     </row>
@@ -16305,10 +16312,10 @@
         <v>35</v>
       </c>
       <c r="B73" s="14" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C73" s="29" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D73" s="16"/>
     </row>
@@ -16317,10 +16324,10 @@
         <v>35</v>
       </c>
       <c r="B74" s="14" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C74" s="36" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D74" s="16"/>
       <c r="E74" s="1"/>
@@ -16343,10 +16350,10 @@
         <v>36</v>
       </c>
       <c r="B75" s="31" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C75" s="37" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D75" s="33"/>
     </row>
@@ -16355,10 +16362,10 @@
         <v>36</v>
       </c>
       <c r="B76" s="14" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C76" s="29" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D76" s="16"/>
     </row>
@@ -16367,10 +16374,10 @@
         <v>36</v>
       </c>
       <c r="B77" s="14" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C77" s="38" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D77" s="16"/>
     </row>
@@ -16379,10 +16386,10 @@
         <v>37</v>
       </c>
       <c r="B78" s="14" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C78" s="29" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D78" s="16"/>
     </row>
@@ -16391,10 +16398,10 @@
         <v>37</v>
       </c>
       <c r="B79" s="31" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C79" s="37" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D79" s="33"/>
     </row>
@@ -16403,10 +16410,10 @@
         <v>38</v>
       </c>
       <c r="B80" s="14" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C80" s="39" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D80" s="16"/>
     </row>
@@ -16415,10 +16422,10 @@
         <v>38</v>
       </c>
       <c r="B81" s="14" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C81" s="39" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D81" s="16"/>
       <c r="E81" s="1"/>
@@ -16441,10 +16448,10 @@
         <v>38</v>
       </c>
       <c r="B82" s="14" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C82" s="39" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D82" s="16"/>
       <c r="E82" s="1"/>
@@ -16467,10 +16474,10 @@
         <v>39</v>
       </c>
       <c r="B83" s="14" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C83" s="40" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D83" s="16"/>
       <c r="E83" s="1"/>
@@ -16493,10 +16500,10 @@
         <v>39</v>
       </c>
       <c r="B84" s="14" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C84" s="39" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D84" s="16"/>
       <c r="E84" s="1"/>
@@ -16519,10 +16526,10 @@
         <v>39</v>
       </c>
       <c r="B85" s="31" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C85" s="41" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D85" s="33"/>
     </row>
@@ -16531,10 +16538,10 @@
         <v>40</v>
       </c>
       <c r="B86" s="31" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C86" s="42" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D86" s="33"/>
     </row>
@@ -16543,10 +16550,10 @@
         <v>40</v>
       </c>
       <c r="B87" s="31" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C87" s="41" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D87" s="33"/>
     </row>
@@ -16555,10 +16562,10 @@
         <v>40</v>
       </c>
       <c r="B88" s="14" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C88" s="39" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D88" s="16"/>
       <c r="E88" s="1"/>
@@ -16581,10 +16588,10 @@
         <v>41</v>
       </c>
       <c r="B89" s="14" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C89" s="40" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D89" s="16"/>
     </row>
@@ -16593,10 +16600,10 @@
         <v>41</v>
       </c>
       <c r="B90" s="31" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C90" s="42" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D90" s="33"/>
     </row>
@@ -16605,10 +16612,10 @@
         <v>41</v>
       </c>
       <c r="B91" s="14" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C91" s="39" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D91" s="16"/>
       <c r="E91" s="1"/>
@@ -16631,10 +16638,10 @@
         <v>42</v>
       </c>
       <c r="B92" s="14" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C92" s="40" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D92" s="16"/>
       <c r="E92" s="1"/>
@@ -16657,10 +16664,10 @@
         <v>43</v>
       </c>
       <c r="B93" s="31" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C93" s="42" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D93" s="33"/>
     </row>
@@ -16669,10 +16676,10 @@
         <v>43</v>
       </c>
       <c r="B94" s="31" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C94" s="41" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D94" s="33"/>
     </row>
@@ -16681,10 +16688,10 @@
         <v>43</v>
       </c>
       <c r="B95" s="14" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C95" s="39" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D95" s="16"/>
       <c r="E95" s="1"/>
@@ -16707,10 +16714,10 @@
         <v>44</v>
       </c>
       <c r="B96" s="14" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C96" s="39" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D96" s="16"/>
       <c r="E96" s="1"/>
@@ -16733,10 +16740,10 @@
         <v>44</v>
       </c>
       <c r="B97" s="31" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C97" s="42" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D97" s="33"/>
     </row>
@@ -16745,10 +16752,10 @@
         <v>47</v>
       </c>
       <c r="B98" s="31" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C98" s="42" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D98" s="16"/>
       <c r="E98" s="1"/>
@@ -16771,10 +16778,10 @@
         <v>48</v>
       </c>
       <c r="B99" s="14" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C99" s="40" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D99" s="16"/>
       <c r="E99" s="1"/>
@@ -16797,13 +16804,13 @@
         <v>49</v>
       </c>
       <c r="B100" s="31" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C100" s="42" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D100" s="33" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="101" s="1" customFormat="1" ht="28.8" spans="1:18">
@@ -16811,10 +16818,10 @@
         <v>52</v>
       </c>
       <c r="B101" s="14" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C101" s="40" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D101" s="16"/>
     </row>
@@ -16823,10 +16830,10 @@
         <v>52</v>
       </c>
       <c r="B102" s="14" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C102" s="40" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D102" s="16"/>
       <c r="E102" s="1"/>
@@ -16849,10 +16856,10 @@
         <v>53</v>
       </c>
       <c r="B103" s="31" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C103" s="42" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D103" s="33"/>
     </row>
@@ -16861,10 +16868,10 @@
         <v>54</v>
       </c>
       <c r="B104" s="14" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C104" s="40" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D104" s="16"/>
     </row>
@@ -16873,10 +16880,10 @@
         <v>55</v>
       </c>
       <c r="B105" s="14" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C105" s="40" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D105" s="16"/>
     </row>
@@ -16885,10 +16892,10 @@
         <v>56</v>
       </c>
       <c r="B106" s="31" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C106" s="42" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D106" s="33"/>
     </row>
@@ -16897,10 +16904,10 @@
         <v>58</v>
       </c>
       <c r="B107" s="31" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C107" s="42" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D107" s="16"/>
       <c r="E107" s="1"/>
@@ -16923,10 +16930,10 @@
         <v>59</v>
       </c>
       <c r="B108" s="14" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C108" s="39" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D108" s="16"/>
       <c r="E108" s="1"/>
@@ -16949,10 +16956,10 @@
         <v>59</v>
       </c>
       <c r="B109" s="14" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C109" s="39" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D109" s="16"/>
       <c r="E109" s="1"/>
@@ -16975,10 +16982,10 @@
         <v>61</v>
       </c>
       <c r="B110" s="14" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C110" s="39" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D110" s="16"/>
       <c r="E110" s="1"/>
@@ -17001,10 +17008,10 @@
         <v>61</v>
       </c>
       <c r="B111" s="14" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C111" s="39" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D111" s="16"/>
       <c r="E111" s="1"/>
@@ -17027,10 +17034,10 @@
         <v>62</v>
       </c>
       <c r="B112" s="14" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C112" s="39" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D112" s="16"/>
       <c r="E112" s="1"/>
@@ -17053,10 +17060,10 @@
         <v>63</v>
       </c>
       <c r="B113" s="14" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C113" s="39" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D113" s="16"/>
       <c r="E113" s="1"/>
@@ -17079,10 +17086,10 @@
         <v>64</v>
       </c>
       <c r="B114" s="43" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C114" s="22" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D114" s="44"/>
       <c r="E114" s="1"/>
@@ -17105,10 +17112,10 @@
         <v>64</v>
       </c>
       <c r="B115" s="14" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C115" s="40" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D115" s="16"/>
       <c r="E115" s="1"/>
@@ -17131,10 +17138,10 @@
         <v>64</v>
       </c>
       <c r="B116" s="14" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C116" s="39" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D116" s="16"/>
       <c r="E116" s="1"/>
@@ -17157,10 +17164,10 @@
         <v>65</v>
       </c>
       <c r="B117" s="14" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C117" s="40" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D117" s="16"/>
       <c r="E117" s="1"/>
@@ -17183,10 +17190,10 @@
         <v>66</v>
       </c>
       <c r="B118" s="14" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C118" s="39" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D118" s="16"/>
       <c r="E118" s="1"/>
@@ -17209,10 +17216,10 @@
         <v>67</v>
       </c>
       <c r="B119" s="14" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C119" s="39" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D119" s="16"/>
       <c r="E119" s="1"/>
@@ -17235,10 +17242,10 @@
         <v>67</v>
       </c>
       <c r="B120" s="14" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C120" s="39" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D120" s="16"/>
       <c r="E120" s="1"/>
@@ -17261,10 +17268,10 @@
         <v>67</v>
       </c>
       <c r="B121" s="14" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C121" s="39" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D121" s="16"/>
       <c r="E121" s="1"/>
@@ -17287,10 +17294,10 @@
         <v>67</v>
       </c>
       <c r="B122" s="14" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C122" s="39" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D122" s="16"/>
       <c r="E122" s="1"/>
@@ -17313,10 +17320,10 @@
         <v>68</v>
       </c>
       <c r="B123" s="31" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C123" s="42" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D123" s="33"/>
     </row>
@@ -17325,10 +17332,10 @@
         <v>68</v>
       </c>
       <c r="B124" s="31" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C124" s="42" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D124" s="33"/>
     </row>
@@ -17337,10 +17344,10 @@
         <v>68</v>
       </c>
       <c r="B125" s="14" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C125" s="39" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D125" s="16"/>
     </row>
@@ -17349,10 +17356,10 @@
         <v>69</v>
       </c>
       <c r="B126" s="14" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C126" s="39" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D126" s="16"/>
     </row>
@@ -17361,10 +17368,10 @@
         <v>70</v>
       </c>
       <c r="B127" s="14" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C127" s="21" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D127" s="16"/>
     </row>
@@ -17373,10 +17380,10 @@
         <v>71</v>
       </c>
       <c r="B128" s="14" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C128" s="20" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D128" s="16"/>
       <c r="E128" s="1"/>
@@ -17399,10 +17406,10 @@
         <v>73</v>
       </c>
       <c r="B129" s="31" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C129" s="34" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D129" s="33"/>
     </row>
@@ -17411,10 +17418,10 @@
         <v>77</v>
       </c>
       <c r="B130" s="31" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C130" s="34" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D130" s="33"/>
     </row>
@@ -17423,10 +17430,10 @@
         <v>78</v>
       </c>
       <c r="B131" s="31" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C131" s="34" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D131" s="33"/>
     </row>
@@ -17435,13 +17442,13 @@
         <v>79</v>
       </c>
       <c r="B132" s="31" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C132" s="34" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D132" s="33" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="133" s="1" customFormat="1" ht="43.2" spans="1:4">
@@ -17449,10 +17456,10 @@
         <v>81</v>
       </c>
       <c r="B133" s="14" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C133" s="20" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D133" s="16"/>
     </row>
@@ -17461,10 +17468,10 @@
         <v>81</v>
       </c>
       <c r="B134" s="31" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C134" s="34" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D134" s="16"/>
     </row>
@@ -17473,10 +17480,10 @@
         <v>82</v>
       </c>
       <c r="B135" s="14" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C135" s="20" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D135" s="16"/>
     </row>
@@ -17485,10 +17492,10 @@
         <v>83</v>
       </c>
       <c r="B136" s="14" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C136" s="20" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D136" s="16"/>
     </row>
@@ -17497,13 +17504,13 @@
         <v>84</v>
       </c>
       <c r="B137" s="31" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C137" s="34" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D137" s="33" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="138" s="1" customFormat="1" ht="25.8" spans="1:4">
@@ -17511,10 +17518,10 @@
         <v>89</v>
       </c>
       <c r="B138" s="14" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C138" s="21" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D138" s="16"/>
     </row>
@@ -17523,10 +17530,10 @@
         <v>90</v>
       </c>
       <c r="B139" s="14" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C139" s="20" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D139" s="16"/>
     </row>
@@ -17535,10 +17542,10 @@
         <v>92</v>
       </c>
       <c r="B140" s="14" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C140" s="20" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D140" s="16"/>
     </row>
@@ -17547,10 +17554,10 @@
         <v>93</v>
       </c>
       <c r="B141" s="14" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C141" s="20" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D141" s="16"/>
     </row>
@@ -17559,10 +17566,10 @@
         <v>94</v>
       </c>
       <c r="B142" s="14" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C142" s="20" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D142" s="16"/>
     </row>
@@ -17571,10 +17578,10 @@
         <v>94</v>
       </c>
       <c r="B143" s="14" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C143" s="20" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D143" s="16"/>
     </row>
@@ -17583,10 +17590,10 @@
         <v>94</v>
       </c>
       <c r="B144" s="14" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C144" s="21" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D144" s="16"/>
     </row>
@@ -17595,10 +17602,10 @@
         <v>95</v>
       </c>
       <c r="B145" s="14" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C145" s="20" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D145" s="16"/>
     </row>
@@ -17607,10 +17614,10 @@
         <v>95</v>
       </c>
       <c r="B146" s="14" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C146" s="21" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D146" s="16"/>
     </row>
@@ -17619,10 +17626,10 @@
         <v>96</v>
       </c>
       <c r="B147" s="14" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C147" s="20" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D147" s="16"/>
       <c r="E147" s="1"/>
@@ -17645,10 +17652,10 @@
         <v>97</v>
       </c>
       <c r="B148" s="31" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C148" s="34" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D148" s="33"/>
     </row>
@@ -17657,10 +17664,10 @@
         <v>98</v>
       </c>
       <c r="B149" s="45" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C149" s="35" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D149" s="46"/>
       <c r="E149" s="47"/>
@@ -17683,10 +17690,10 @@
         <v>98</v>
       </c>
       <c r="B150" s="31" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C150" s="34" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D150" s="33"/>
     </row>
@@ -17695,10 +17702,10 @@
         <v>98</v>
       </c>
       <c r="B151" s="14" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C151" s="20" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D151" s="16"/>
     </row>
@@ -17707,10 +17714,10 @@
         <v>99</v>
       </c>
       <c r="B152" s="14" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C152" s="20" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D152" s="16"/>
     </row>
@@ -17719,10 +17726,10 @@
         <v>100</v>
       </c>
       <c r="B153" s="14" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C153" s="20" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D153" s="16"/>
     </row>
@@ -17731,10 +17738,10 @@
         <v>100</v>
       </c>
       <c r="B154" s="14" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C154" s="20" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D154" s="16"/>
     </row>
@@ -17743,10 +17750,10 @@
         <v>101</v>
       </c>
       <c r="B155" s="43" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C155" s="22" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D155" s="48"/>
       <c r="E155" s="49"/>
@@ -17769,13 +17776,13 @@
         <v>103</v>
       </c>
       <c r="B156" s="45" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C156" s="35" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D156" s="46" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="E156" s="47"/>
       <c r="F156" s="47"/>
@@ -17797,10 +17804,10 @@
         <v>104</v>
       </c>
       <c r="B157" s="43" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C157" s="22" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D157" s="48"/>
       <c r="E157" s="49"/>
@@ -17823,10 +17830,10 @@
         <v>105</v>
       </c>
       <c r="B158" s="43" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C158" s="22" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D158" s="48"/>
       <c r="E158" s="49"/>
@@ -17849,10 +17856,10 @@
         <v>105</v>
       </c>
       <c r="B159" s="43" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C159" s="22" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D159" s="48"/>
       <c r="E159" s="49"/>
@@ -17875,10 +17882,10 @@
         <v>107</v>
       </c>
       <c r="B160" s="43" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C160" s="29" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D160" s="48"/>
       <c r="E160" s="49"/>
@@ -17901,10 +17908,10 @@
         <v>107</v>
       </c>
       <c r="B161" s="43" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C161" s="22" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D161" s="48"/>
       <c r="E161" s="49"/>
@@ -17927,10 +17934,10 @@
         <v>107</v>
       </c>
       <c r="B162" s="43" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C162" s="22" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D162" s="48"/>
       <c r="E162" s="49"/>
@@ -17953,10 +17960,10 @@
         <v>108</v>
       </c>
       <c r="B163" s="45" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C163" s="35" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D163" s="46"/>
       <c r="E163" s="47"/>
@@ -17979,10 +17986,10 @@
         <v>108</v>
       </c>
       <c r="B164" s="43" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C164" s="29" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D164" s="48"/>
       <c r="E164" s="49"/>
@@ -18005,10 +18012,10 @@
         <v>108</v>
       </c>
       <c r="B165" s="43" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C165" s="36" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D165" s="48"/>
       <c r="E165" s="49"/>
@@ -18031,10 +18038,10 @@
         <v>108</v>
       </c>
       <c r="B166" s="43" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C166" s="22" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D166" s="48"/>
       <c r="E166" s="49"/>
@@ -18057,10 +18064,10 @@
         <v>108</v>
       </c>
       <c r="B167" s="45" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C167" s="35" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D167" s="46"/>
       <c r="E167" s="47"/>
@@ -18083,10 +18090,10 @@
         <v>109</v>
       </c>
       <c r="B168" s="43" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C168" s="22" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D168" s="48"/>
       <c r="E168" s="49"/>
@@ -18109,10 +18116,10 @@
         <v>109</v>
       </c>
       <c r="B169" s="43" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C169" s="22" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D169" s="48"/>
       <c r="E169" s="49"/>
@@ -18135,10 +18142,10 @@
         <v>110</v>
       </c>
       <c r="B170" s="43" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C170" s="22" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D170" s="48"/>
       <c r="E170" s="49"/>
@@ -18161,13 +18168,13 @@
         <v>112</v>
       </c>
       <c r="B171" s="43" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C171" s="22" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D171" s="48" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E171" s="49"/>
       <c r="F171" s="49"/>
@@ -18189,10 +18196,10 @@
         <v>112</v>
       </c>
       <c r="B172" s="43" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C172" s="22" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D172" s="48"/>
       <c r="E172" s="49"/>
@@ -18215,13 +18222,13 @@
         <v>113</v>
       </c>
       <c r="B173" s="43" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C173" s="22" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D173" s="48" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E173" s="49"/>
       <c r="F173" s="49"/>
@@ -18243,10 +18250,10 @@
         <v>113</v>
       </c>
       <c r="B174" s="43" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C174" s="22" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D174" s="48"/>
       <c r="E174" s="49"/>
@@ -18269,10 +18276,10 @@
         <v>114</v>
       </c>
       <c r="B175" s="43" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C175" s="22" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D175" s="48"/>
       <c r="E175" s="49"/>
@@ -18295,10 +18302,10 @@
         <v>114</v>
       </c>
       <c r="B176" s="45" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C176" s="35" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D176" s="46"/>
       <c r="E176" s="47"/>
@@ -18321,10 +18328,10 @@
         <v>115</v>
       </c>
       <c r="B177" s="43" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C177" s="22" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D177" s="48"/>
       <c r="E177" s="49"/>
@@ -18347,10 +18354,10 @@
         <v>115</v>
       </c>
       <c r="B178" s="45" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C178" s="35" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D178" s="46"/>
       <c r="E178" s="47"/>
@@ -18373,10 +18380,10 @@
         <v>116</v>
       </c>
       <c r="B179" s="45" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C179" s="35" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D179" s="46"/>
       <c r="E179" s="47"/>
@@ -18399,10 +18406,10 @@
         <v>116</v>
       </c>
       <c r="B180" s="43" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C180" s="29" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D180" s="48"/>
       <c r="E180" s="49"/>
@@ -18425,10 +18432,10 @@
         <v>116</v>
       </c>
       <c r="B181" s="43" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C181" s="22" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D181" s="48"/>
       <c r="E181" s="49"/>
@@ -18451,10 +18458,10 @@
         <v>117</v>
       </c>
       <c r="B182" s="43" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C182" s="22" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D182" s="48"/>
       <c r="E182" s="49"/>
@@ -18477,10 +18484,10 @@
         <v>117</v>
       </c>
       <c r="B183" s="43" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C183" s="38" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D183" s="48"/>
       <c r="E183" s="49"/>
@@ -18503,10 +18510,10 @@
         <v>118</v>
       </c>
       <c r="B184" s="43" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C184" s="29" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D184" s="48"/>
       <c r="E184" s="49"/>
@@ -18529,10 +18536,10 @@
         <v>119</v>
       </c>
       <c r="B185" s="43" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C185" s="22" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D185" s="48"/>
       <c r="E185" s="49"/>
@@ -18555,10 +18562,10 @@
         <v>119</v>
       </c>
       <c r="B186" s="43" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C186" s="22" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D186" s="48"/>
       <c r="E186" s="49"/>
@@ -18581,10 +18588,10 @@
         <v>119</v>
       </c>
       <c r="B187" s="43" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C187" s="22" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D187" s="48"/>
       <c r="E187" s="49"/>
@@ -18607,10 +18614,10 @@
         <v>119</v>
       </c>
       <c r="B188" s="43" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C188" s="29" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D188" s="48"/>
       <c r="E188" s="49"/>
@@ -18633,10 +18640,10 @@
         <v>120</v>
       </c>
       <c r="B189" s="43" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C189" s="29" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D189" s="48"/>
       <c r="E189" s="49"/>
@@ -18659,10 +18666,10 @@
         <v>120</v>
       </c>
       <c r="B190" s="43" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C190" s="29" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D190" s="48"/>
       <c r="E190" s="49"/>
@@ -18685,10 +18692,10 @@
         <v>120</v>
       </c>
       <c r="B191" s="43" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C191" s="29" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D191" s="48"/>
       <c r="E191" s="49"/>
@@ -18711,10 +18718,10 @@
         <v>120</v>
       </c>
       <c r="B192" s="43" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C192" s="29" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D192" s="48"/>
       <c r="E192" s="49"/>
@@ -18737,10 +18744,10 @@
         <v>120</v>
       </c>
       <c r="B193" s="43" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C193" s="29" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D193" s="48"/>
       <c r="E193" s="49"/>
@@ -18763,10 +18770,10 @@
         <v>121</v>
       </c>
       <c r="B194" s="43" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C194" s="29" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D194" s="48"/>
       <c r="E194" s="49"/>
@@ -18789,10 +18796,10 @@
         <v>121</v>
       </c>
       <c r="B195" s="45" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C195" s="35" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D195" s="46"/>
       <c r="E195" s="47"/>
@@ -18815,10 +18822,10 @@
         <v>121</v>
       </c>
       <c r="B196" s="43" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C196" s="29" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D196" s="48"/>
       <c r="E196" s="49"/>
@@ -18841,10 +18848,10 @@
         <v>121</v>
       </c>
       <c r="B197" s="43" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C197" s="29" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D197" s="48"/>
       <c r="E197" s="49"/>
@@ -18867,10 +18874,10 @@
         <v>121</v>
       </c>
       <c r="B198" s="43" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C198" s="22" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D198" s="48"/>
       <c r="E198" s="49"/>
@@ -18893,10 +18900,10 @@
         <v>121</v>
       </c>
       <c r="B199" s="43" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C199" s="29" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D199" s="48"/>
       <c r="E199" s="49"/>
@@ -18919,10 +18926,10 @@
         <v>122</v>
       </c>
       <c r="B200" s="43" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C200" s="29" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D200" s="48"/>
       <c r="E200" s="49"/>
@@ -18945,10 +18952,10 @@
         <v>122</v>
       </c>
       <c r="B201" s="43" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C201" s="22" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D201" s="48"/>
       <c r="E201" s="49"/>
@@ -18971,10 +18978,10 @@
         <v>123</v>
       </c>
       <c r="B202" s="45" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C202" s="37" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D202" s="46"/>
       <c r="E202" s="47"/>
@@ -18997,10 +19004,10 @@
         <v>123</v>
       </c>
       <c r="B203" s="43" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C203" s="29" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D203" s="48"/>
       <c r="E203" s="49"/>
@@ -19023,10 +19030,10 @@
         <v>123</v>
       </c>
       <c r="B204" s="43" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C204" s="29" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D204" s="48"/>
       <c r="E204" s="49"/>
@@ -19049,10 +19056,10 @@
         <v>123</v>
       </c>
       <c r="B205" s="43" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C205" s="22" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D205" s="48"/>
       <c r="E205" s="49"/>
@@ -19075,10 +19082,10 @@
         <v>123</v>
       </c>
       <c r="B206" s="43" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C206" s="29" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D206" s="48"/>
       <c r="E206" s="49"/>
@@ -19101,10 +19108,10 @@
         <v>123</v>
       </c>
       <c r="B207" s="43" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C207" s="22" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D207" s="48"/>
       <c r="E207" s="49"/>
@@ -19127,10 +19134,10 @@
         <v>123</v>
       </c>
       <c r="B208" s="43" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C208" s="29" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D208" s="48"/>
       <c r="E208" s="49"/>
@@ -19153,10 +19160,10 @@
         <v>123</v>
       </c>
       <c r="B209" s="43" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C209" s="29" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D209" s="48"/>
       <c r="E209" s="49"/>
@@ -19179,10 +19186,10 @@
         <v>124</v>
       </c>
       <c r="B210" s="43" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C210" s="29" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D210" s="48"/>
       <c r="E210" s="49"/>
@@ -19205,10 +19212,10 @@
         <v>124</v>
       </c>
       <c r="B211" s="43" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C211" s="22" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D211" s="48"/>
       <c r="E211" s="49"/>
@@ -19231,10 +19238,10 @@
         <v>124</v>
       </c>
       <c r="B212" s="43" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C212" s="29" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D212" s="48"/>
       <c r="E212" s="49"/>
@@ -19257,10 +19264,10 @@
         <v>125</v>
       </c>
       <c r="B213" s="43" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C213" s="22" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D213" s="48"/>
       <c r="E213" s="49"/>
@@ -19283,10 +19290,10 @@
         <v>125</v>
       </c>
       <c r="B214" s="43" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C214" s="29" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D214" s="48"/>
       <c r="E214" s="49"/>
@@ -19309,10 +19316,10 @@
         <v>125</v>
       </c>
       <c r="B215" s="43" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C215" s="22" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D215" s="48"/>
       <c r="E215" s="49"/>
@@ -19335,10 +19342,10 @@
         <v>125</v>
       </c>
       <c r="B216" s="43" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C216" s="22" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D216" s="48"/>
       <c r="E216" s="49"/>
@@ -19361,10 +19368,10 @@
         <v>126</v>
       </c>
       <c r="B217" s="43" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C217" s="29" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D217" s="48"/>
       <c r="E217" s="49"/>
@@ -19387,10 +19394,10 @@
         <v>126</v>
       </c>
       <c r="B218" s="43" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C218" s="29" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D218" s="48"/>
       <c r="E218" s="49"/>
@@ -19413,10 +19420,10 @@
         <v>126</v>
       </c>
       <c r="B219" s="43" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C219" s="29" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="D219" s="48"/>
       <c r="E219" s="49"/>
@@ -19439,10 +19446,10 @@
         <v>126</v>
       </c>
       <c r="B220" s="45" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C220" s="35" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D220" s="46"/>
       <c r="E220" s="47"/>
@@ -19465,10 +19472,10 @@
         <v>127</v>
       </c>
       <c r="B221" s="43" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C221" s="22" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="D221" s="48"/>
       <c r="E221" s="49"/>
@@ -19491,10 +19498,10 @@
         <v>127</v>
       </c>
       <c r="B222" s="43" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C222" s="22" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="D222" s="48"/>
       <c r="E222" s="49"/>
@@ -19517,10 +19524,10 @@
         <v>127</v>
       </c>
       <c r="B223" s="45" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C223" s="35" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="D223" s="46"/>
       <c r="E223" s="47"/>
@@ -19543,10 +19550,10 @@
         <v>127</v>
       </c>
       <c r="B224" s="43" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C224" s="36" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D224" s="48"/>
       <c r="E224" s="49"/>
@@ -19569,10 +19576,10 @@
         <v>128</v>
       </c>
       <c r="B225" s="43" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C225" s="29" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="D225" s="48"/>
       <c r="E225" s="49"/>
@@ -19595,10 +19602,10 @@
         <v>128</v>
       </c>
       <c r="B226" s="43" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C226" s="22" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D226" s="48"/>
       <c r="E226" s="49"/>
@@ -19621,10 +19628,10 @@
         <v>129</v>
       </c>
       <c r="B227" s="45" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C227" s="35" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D227" s="46"/>
       <c r="E227" s="47"/>
@@ -19647,10 +19654,10 @@
         <v>129</v>
       </c>
       <c r="B228" s="43" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C228" s="29" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D228" s="48"/>
       <c r="E228" s="49"/>
@@ -19673,10 +19680,10 @@
         <v>129</v>
       </c>
       <c r="B229" s="43" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C229" s="22" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D229" s="48"/>
       <c r="E229" s="49"/>
@@ -19699,10 +19706,10 @@
         <v>129</v>
       </c>
       <c r="B230" s="43" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C230" s="29" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D230" s="48"/>
       <c r="E230" s="49"/>
@@ -19725,10 +19732,10 @@
         <v>129</v>
       </c>
       <c r="B231" s="43" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C231" s="29" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D231" s="48"/>
       <c r="E231" s="49"/>
@@ -19751,10 +19758,10 @@
         <v>129</v>
       </c>
       <c r="B232" s="43" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C232" s="29" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="D232" s="48"/>
       <c r="E232" s="49"/>
@@ -19777,10 +19784,10 @@
         <v>130</v>
       </c>
       <c r="B233" s="43" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C233" s="22" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D233" s="48"/>
       <c r="E233" s="49"/>
@@ -19803,10 +19810,10 @@
         <v>130</v>
       </c>
       <c r="B234" s="43" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C234" s="22" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D234" s="48"/>
       <c r="E234" s="49"/>
@@ -19829,10 +19836,10 @@
         <v>130</v>
       </c>
       <c r="B235" s="43" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C235" s="38" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="D235" s="48"/>
       <c r="E235" s="49"/>
@@ -19855,10 +19862,10 @@
         <v>131</v>
       </c>
       <c r="B236" s="43" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C236" s="36" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D236" s="48"/>
       <c r="E236" s="49"/>
@@ -19881,10 +19888,10 @@
         <v>132</v>
       </c>
       <c r="B237" s="43" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C237" s="29" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D237" s="48"/>
       <c r="E237" s="49"/>
@@ -19907,10 +19914,10 @@
         <v>132</v>
       </c>
       <c r="B238" s="43" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C238" s="29" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D238" s="48"/>
       <c r="E238" s="49"/>
@@ -19933,10 +19940,10 @@
         <v>132</v>
       </c>
       <c r="B239" s="45" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C239" s="35" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="D239" s="46"/>
       <c r="E239" s="47"/>
@@ -19959,10 +19966,10 @@
         <v>132</v>
       </c>
       <c r="B240" s="43" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C240" s="29" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="D240" s="48"/>
       <c r="E240" s="49"/>
@@ -19985,10 +19992,10 @@
         <v>133</v>
       </c>
       <c r="B241" s="43" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C241" s="29" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D241" s="48"/>
       <c r="E241" s="49"/>
@@ -20011,10 +20018,10 @@
         <v>133</v>
       </c>
       <c r="B242" s="43" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C242" s="29" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="D242" s="48"/>
       <c r="E242" s="49"/>
@@ -20037,10 +20044,10 @@
         <v>133</v>
       </c>
       <c r="B243" s="43" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C243" s="29" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="D243" s="48"/>
       <c r="E243" s="49"/>
@@ -20063,10 +20070,10 @@
         <v>133</v>
       </c>
       <c r="B244" s="43" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C244" s="22" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="D244" s="48"/>
       <c r="E244" s="49"/>
@@ -20089,10 +20096,10 @@
         <v>133</v>
       </c>
       <c r="B245" s="43" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C245" s="22" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D245" s="48"/>
       <c r="E245" s="49"/>
@@ -20115,10 +20122,10 @@
         <v>133</v>
       </c>
       <c r="B246" s="43" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C246" s="29" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="D246" s="48"/>
       <c r="E246" s="49"/>
@@ -20141,10 +20148,10 @@
         <v>134</v>
       </c>
       <c r="B247" s="43" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C247" s="29" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="D247" s="44"/>
       <c r="E247" s="49"/>
@@ -20167,10 +20174,10 @@
         <v>135</v>
       </c>
       <c r="B248" s="43" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C248" s="29" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D248" s="44"/>
       <c r="E248" s="1"/>
@@ -20193,10 +20200,10 @@
         <v>135</v>
       </c>
       <c r="B249" s="43" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C249" s="29" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="D249" s="44"/>
       <c r="E249" s="1"/>
@@ -20219,10 +20226,10 @@
         <v>135</v>
       </c>
       <c r="B250" s="45" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C250" s="37" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D250" s="51"/>
     </row>
@@ -20231,10 +20238,10 @@
         <v>135</v>
       </c>
       <c r="B251" s="43" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C251" s="22" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="D251" s="44"/>
     </row>
@@ -20243,10 +20250,10 @@
         <v>135</v>
       </c>
       <c r="B252" s="45" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C252" s="35" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="D252" s="51"/>
     </row>
@@ -20255,10 +20262,10 @@
         <v>136</v>
       </c>
       <c r="B253" s="43" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C253" s="29" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="D253" s="44"/>
       <c r="E253" s="1"/>
@@ -20281,10 +20288,10 @@
         <v>136</v>
       </c>
       <c r="B254" s="43" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C254" s="29" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D254" s="44"/>
       <c r="E254" s="1"/>
@@ -20307,10 +20314,10 @@
         <v>136</v>
       </c>
       <c r="B255" s="43" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C255" s="22" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="D255" s="44"/>
     </row>
@@ -20319,10 +20326,10 @@
         <v>136</v>
       </c>
       <c r="B256" s="43" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C256" s="29" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D256" s="44"/>
     </row>
@@ -20331,10 +20338,10 @@
         <v>137</v>
       </c>
       <c r="B257" s="45" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C257" s="35" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="D257" s="51"/>
     </row>
@@ -20343,10 +20350,10 @@
         <v>137</v>
       </c>
       <c r="B258" s="43" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C258" s="29" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D258" s="44"/>
     </row>
@@ -20355,10 +20362,10 @@
         <v>137</v>
       </c>
       <c r="B259" s="43" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C259" s="29" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D259" s="44"/>
     </row>
@@ -20367,10 +20374,10 @@
         <v>137</v>
       </c>
       <c r="B260" s="43" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C260" s="22" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="D260" s="44"/>
     </row>
@@ -20379,10 +20386,10 @@
         <v>137</v>
       </c>
       <c r="B261" s="45" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C261" s="37" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="D261" s="51"/>
     </row>
@@ -20391,10 +20398,10 @@
         <v>137</v>
       </c>
       <c r="B262" s="43" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C262" s="29" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D262" s="44"/>
       <c r="E262" s="1"/>
@@ -20417,10 +20424,10 @@
         <v>138</v>
       </c>
       <c r="B263" s="43" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C263" s="29" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D263" s="44"/>
     </row>
@@ -20429,10 +20436,10 @@
         <v>138</v>
       </c>
       <c r="B264" s="43" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C264" s="22" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D264" s="44"/>
     </row>
@@ -20441,10 +20448,10 @@
         <v>138</v>
       </c>
       <c r="B265" s="43" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C265" s="29" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="D265" s="44"/>
     </row>
@@ -20453,10 +20460,10 @@
         <v>138</v>
       </c>
       <c r="B266" s="43" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C266" s="29" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="D266" s="44"/>
     </row>
@@ -20465,10 +20472,10 @@
         <v>139</v>
       </c>
       <c r="B267" s="43" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C267" s="22" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="D267" s="44"/>
     </row>
@@ -20477,10 +20484,10 @@
         <v>139</v>
       </c>
       <c r="B268" s="43" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C268" s="29" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D268" s="44"/>
     </row>
@@ -20489,10 +20496,10 @@
         <v>139</v>
       </c>
       <c r="B269" s="43" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C269" s="29" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="D269" s="44"/>
       <c r="E269" s="1"/>
@@ -20515,10 +20522,10 @@
         <v>140</v>
       </c>
       <c r="B270" s="43" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C270" s="29" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="D270" s="44"/>
       <c r="E270" s="1"/>
@@ -20541,10 +20548,10 @@
         <v>140</v>
       </c>
       <c r="B271" s="43" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C271" s="29" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="D271" s="44"/>
     </row>
@@ -20553,10 +20560,10 @@
         <v>140</v>
       </c>
       <c r="B272" s="43" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C272" s="22" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D272" s="44"/>
     </row>
@@ -20565,10 +20572,10 @@
         <v>140</v>
       </c>
       <c r="B273" s="43" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C273" s="29" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="D273" s="44"/>
     </row>
@@ -20577,10 +20584,10 @@
         <v>141</v>
       </c>
       <c r="B274" s="45" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C274" s="35" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="D274" s="51"/>
     </row>
@@ -20589,10 +20596,10 @@
         <v>141</v>
       </c>
       <c r="B275" s="43" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C275" s="29" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="D275" s="44"/>
     </row>
@@ -20601,10 +20608,10 @@
         <v>141</v>
       </c>
       <c r="B276" s="43" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C276" s="22" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="D276" s="44"/>
     </row>
@@ -20613,10 +20620,10 @@
         <v>141</v>
       </c>
       <c r="B277" s="45" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C277" s="37" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="D277" s="51"/>
     </row>
@@ -20625,10 +20632,10 @@
         <v>141</v>
       </c>
       <c r="B278" s="45" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C278" s="37" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="D278" s="51"/>
     </row>
@@ -20637,10 +20644,10 @@
         <v>143</v>
       </c>
       <c r="B279" s="43" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C279" s="29" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D279" s="44"/>
     </row>
@@ -20649,10 +20656,10 @@
         <v>143</v>
       </c>
       <c r="B280" s="43" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C280" s="22" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="D280" s="44"/>
     </row>
@@ -20661,10 +20668,10 @@
         <v>143</v>
       </c>
       <c r="B281" s="43" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C281" s="22" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="D281" s="44"/>
     </row>
@@ -20673,10 +20680,10 @@
         <v>143</v>
       </c>
       <c r="B282" s="43" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C282" s="29" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="D282" s="44"/>
     </row>
@@ -20685,10 +20692,10 @@
         <v>144</v>
       </c>
       <c r="B283" s="43" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C283" s="29" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="D283" s="44"/>
     </row>
@@ -20697,10 +20704,10 @@
         <v>144</v>
       </c>
       <c r="B284" s="43" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C284" s="22" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="D284" s="44"/>
     </row>
@@ -20709,10 +20716,10 @@
         <v>144</v>
       </c>
       <c r="B285" s="43" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C285" s="29" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="D285" s="44"/>
     </row>
@@ -20721,10 +20728,10 @@
         <v>144</v>
       </c>
       <c r="B286" s="43" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C286" s="29" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="D286" s="44"/>
     </row>
@@ -20733,10 +20740,10 @@
         <v>145</v>
       </c>
       <c r="B287" s="43" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C287" s="22" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="D287" s="44"/>
     </row>
@@ -20745,10 +20752,10 @@
         <v>145</v>
       </c>
       <c r="B288" s="43" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C288" s="22" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="D288" s="44"/>
     </row>
@@ -20757,10 +20764,10 @@
         <v>145</v>
       </c>
       <c r="B289" s="43" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C289" s="29" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="D289" s="44"/>
     </row>
@@ -20769,10 +20776,10 @@
         <v>145</v>
       </c>
       <c r="B290" s="45" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C290" s="35" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="D290" s="51"/>
     </row>
@@ -20781,13 +20788,13 @@
         <v>146</v>
       </c>
       <c r="B291" s="43" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C291" s="29" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="D291" s="44" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="292" s="4" customFormat="1" spans="1:4">
@@ -20795,10 +20802,10 @@
         <v>146</v>
       </c>
       <c r="B292" s="45" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C292" s="37" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="D292" s="51"/>
     </row>
@@ -20807,10 +20814,10 @@
         <v>146</v>
       </c>
       <c r="B293" s="43" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C293" s="22" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="D293" s="44"/>
     </row>
@@ -20819,10 +20826,10 @@
         <v>147</v>
       </c>
       <c r="B294" s="43" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C294" s="22" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="D294" s="44"/>
     </row>
@@ -20831,10 +20838,10 @@
         <v>147</v>
       </c>
       <c r="B295" s="43" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C295" s="22" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="D295" s="52"/>
     </row>
@@ -20843,10 +20850,10 @@
         <v>147</v>
       </c>
       <c r="B296" s="45" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C296" s="37" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="D296" s="53"/>
     </row>
@@ -20855,10 +20862,10 @@
         <v>147</v>
       </c>
       <c r="B297" s="43" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C297" s="22" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="D297" s="44"/>
     </row>
@@ -20867,10 +20874,10 @@
         <v>148</v>
       </c>
       <c r="B298" s="45" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C298" s="37" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="D298" s="53"/>
     </row>
@@ -20879,10 +20886,10 @@
         <v>148</v>
       </c>
       <c r="B299" s="45" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C299" s="37" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="D299" s="53"/>
     </row>
@@ -20891,10 +20898,10 @@
         <v>148</v>
       </c>
       <c r="B300" s="45" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C300" s="35" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="D300" s="53"/>
     </row>
@@ -20903,10 +20910,10 @@
         <v>148</v>
       </c>
       <c r="B301" s="45" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C301" s="37" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="D301" s="53"/>
     </row>
@@ -20915,10 +20922,10 @@
         <v>149</v>
       </c>
       <c r="B302" s="45" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C302" s="37" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="D302" s="53"/>
     </row>
@@ -20927,10 +20934,10 @@
         <v>149</v>
       </c>
       <c r="B303" s="45" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C303" s="37" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="D303" s="53"/>
     </row>
@@ -20939,10 +20946,10 @@
         <v>149</v>
       </c>
       <c r="B304" s="45" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C304" s="37" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="D304" s="53"/>
     </row>
@@ -20951,10 +20958,10 @@
         <v>149</v>
       </c>
       <c r="B305" s="43" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C305" s="29" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="D305" s="52"/>
     </row>
@@ -20963,10 +20970,10 @@
         <v>150</v>
       </c>
       <c r="B306" s="45" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C306" s="37" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="D306" s="53"/>
     </row>
@@ -20975,10 +20982,10 @@
         <v>151</v>
       </c>
       <c r="B307" s="45" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C307" s="35" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="D307" s="53"/>
     </row>
@@ -20987,10 +20994,10 @@
         <v>152</v>
       </c>
       <c r="B308" s="43" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C308" s="29" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="D308" s="52"/>
     </row>
@@ -20999,10 +21006,10 @@
         <v>152</v>
       </c>
       <c r="B309" s="43" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C309" s="22" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="D309" s="52"/>
     </row>
@@ -21011,10 +21018,10 @@
         <v>152</v>
       </c>
       <c r="B310" s="45" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C310" s="35" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="D310" s="53"/>
     </row>
@@ -21023,10 +21030,10 @@
         <v>152</v>
       </c>
       <c r="B311" s="43" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C311" s="29" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="D311" s="52"/>
     </row>
@@ -21035,10 +21042,10 @@
         <v>153</v>
       </c>
       <c r="B312" s="43" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C312" s="22" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="D312" s="52"/>
     </row>
@@ -21047,10 +21054,10 @@
         <v>153</v>
       </c>
       <c r="B313" s="45" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="C313" s="35" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="D313" s="53"/>
     </row>
@@ -21059,10 +21066,10 @@
         <v>153</v>
       </c>
       <c r="B314" s="45" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C314" s="37" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="D314" s="53"/>
     </row>
@@ -21071,10 +21078,10 @@
         <v>154</v>
       </c>
       <c r="B315" s="43" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C315" s="22" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="D315" s="52"/>
       <c r="E315" s="1"/>
@@ -21097,10 +21104,10 @@
         <v>155</v>
       </c>
       <c r="B316" s="45" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C316" s="35" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="D316" s="53"/>
     </row>
@@ -21109,10 +21116,10 @@
         <v>156</v>
       </c>
       <c r="B317" s="45" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C317" s="37" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="D317" s="53"/>
     </row>
@@ -21121,10 +21128,10 @@
         <v>156</v>
       </c>
       <c r="B318" s="43" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C318" s="22" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="D318" s="52"/>
     </row>
@@ -21133,10 +21140,10 @@
         <v>156</v>
       </c>
       <c r="B319" s="45" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C319" s="35" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="D319" s="53"/>
     </row>
@@ -21145,10 +21152,10 @@
         <v>161</v>
       </c>
       <c r="B320" s="45" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C320" s="35" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="D320" s="53"/>
     </row>
@@ -21157,10 +21164,10 @@
         <v>161</v>
       </c>
       <c r="B321" s="43" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C321" s="29" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="D321" s="52"/>
     </row>
@@ -21169,10 +21176,10 @@
         <v>161</v>
       </c>
       <c r="B322" s="43" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C322" s="22" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="D322" s="52"/>
     </row>
@@ -21181,10 +21188,10 @@
         <v>162</v>
       </c>
       <c r="B323" s="43" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C323" s="29" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="D323" s="52"/>
     </row>
@@ -21193,10 +21200,10 @@
         <v>162</v>
       </c>
       <c r="B324" s="45" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C324" s="35" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="D324" s="53"/>
     </row>
@@ -21205,10 +21212,10 @@
         <v>162</v>
       </c>
       <c r="B325" s="43" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C325" s="29" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="D325" s="52"/>
     </row>
@@ -21217,10 +21224,10 @@
         <v>162</v>
       </c>
       <c r="B326" s="45" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C326" s="35" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="D326" s="53"/>
     </row>
@@ -21229,10 +21236,10 @@
         <v>163</v>
       </c>
       <c r="B327" s="45" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C327" s="37" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="D327" s="53"/>
     </row>
@@ -21241,10 +21248,10 @@
         <v>163</v>
       </c>
       <c r="B328" s="45" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="C328" s="35" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="D328" s="53"/>
     </row>
@@ -21253,10 +21260,10 @@
         <v>163</v>
       </c>
       <c r="B329" s="45" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C329" s="35" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="D329" s="53"/>
     </row>
@@ -21265,10 +21272,10 @@
         <v>164</v>
       </c>
       <c r="B330" s="43" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C330" s="22" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="D330" s="52"/>
       <c r="E330" s="1"/>
@@ -21291,10 +21298,10 @@
         <v>164</v>
       </c>
       <c r="B331" s="45" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C331" s="35" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="D331" s="52"/>
     </row>
@@ -21303,10 +21310,10 @@
         <v>165</v>
       </c>
       <c r="B332" s="43" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C332" s="22" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="D332" s="52"/>
       <c r="E332" s="1"/>
@@ -21329,10 +21336,10 @@
         <v>166</v>
       </c>
       <c r="B333" s="45" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C333" s="35" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="D333" s="52"/>
     </row>
@@ -21341,13 +21348,13 @@
         <v>166</v>
       </c>
       <c r="B334" s="45" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="C334" s="35" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="D334" s="33" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
     </row>
     <row r="335" s="1" customFormat="1" ht="144" spans="1:18">
@@ -21355,10 +21362,10 @@
         <v>166</v>
       </c>
       <c r="B335" s="45" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C335" s="35" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="D335" s="33"/>
     </row>
@@ -21367,10 +21374,10 @@
         <v>166</v>
       </c>
       <c r="B336" s="45" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="C336" s="35" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="D336" s="53"/>
     </row>
@@ -21379,10 +21386,10 @@
         <v>167</v>
       </c>
       <c r="B337" s="45" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="C337" s="35" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="D337" s="16"/>
       <c r="E337" s="1"/>
@@ -21405,10 +21412,10 @@
         <v>167</v>
       </c>
       <c r="B338" s="43" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="C338" s="22" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="D338" s="16"/>
     </row>
@@ -21417,10 +21424,10 @@
         <v>169</v>
       </c>
       <c r="B339" s="43" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C339" s="22" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="D339" s="16"/>
       <c r="E339" s="1"/>
@@ -21443,10 +21450,10 @@
         <v>169</v>
       </c>
       <c r="B340" s="43" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C340" s="29" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="D340" s="16"/>
     </row>
@@ -21455,10 +21462,10 @@
         <v>169</v>
       </c>
       <c r="B341" s="43" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C341" s="22" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="D341" s="16"/>
       <c r="E341" s="1"/>
@@ -21481,10 +21488,10 @@
         <v>170</v>
       </c>
       <c r="B342" s="45" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="C342" s="35" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="D342" s="16"/>
     </row>
@@ -21493,10 +21500,10 @@
         <v>170</v>
       </c>
       <c r="B343" s="45" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="C343" s="35" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="D343" s="16"/>
     </row>
@@ -21505,10 +21512,10 @@
         <v>170</v>
       </c>
       <c r="B344" s="43" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C344" s="29" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="D344" s="16"/>
     </row>
@@ -21517,10 +21524,10 @@
         <v>171</v>
       </c>
       <c r="B345" s="45" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C345" s="37" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="D345" s="16"/>
     </row>
@@ -21529,10 +21536,10 @@
         <v>172</v>
       </c>
       <c r="B346" s="43" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C346" s="29" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="D346" s="16"/>
     </row>
@@ -21541,10 +21548,10 @@
         <v>172</v>
       </c>
       <c r="B347" s="45" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="C347" s="37" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="D347" s="16"/>
     </row>
@@ -21553,10 +21560,10 @@
         <v>172</v>
       </c>
       <c r="B348" s="43" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="C348" s="29" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="D348" s="16"/>
       <c r="E348" s="1"/>
@@ -21579,10 +21586,10 @@
         <v>172</v>
       </c>
       <c r="B349" s="45" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="C349" s="37" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="D349" s="16"/>
     </row>
@@ -21591,10 +21598,10 @@
         <v>172</v>
       </c>
       <c r="B350" s="43" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="C350" s="22" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="D350" s="16"/>
     </row>
@@ -21603,10 +21610,10 @@
         <v>173</v>
       </c>
       <c r="B351" s="45" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C351" s="35" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="D351" s="16"/>
     </row>
@@ -21615,10 +21622,10 @@
         <v>173</v>
       </c>
       <c r="B352" s="43" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="C352" s="22" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="D352" s="16"/>
       <c r="E352" s="1"/>
@@ -21641,10 +21648,10 @@
         <v>173</v>
       </c>
       <c r="B353" s="43" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="C353" s="29" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="D353" s="16"/>
     </row>
@@ -21653,10 +21660,10 @@
         <v>173</v>
       </c>
       <c r="B354" s="45" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="C354" s="35" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="D354" s="16"/>
     </row>
@@ -21665,10 +21672,10 @@
         <v>174</v>
       </c>
       <c r="B355" s="45" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="C355" s="35" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="D355" s="16"/>
     </row>
@@ -21677,10 +21684,10 @@
         <v>174</v>
       </c>
       <c r="B356" s="45" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="C356" s="35" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="D356" s="16"/>
     </row>
@@ -21689,10 +21696,10 @@
         <v>174</v>
       </c>
       <c r="B357" s="43" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="C357" s="22" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="D357" s="16"/>
     </row>
@@ -21701,10 +21708,10 @@
         <v>175</v>
       </c>
       <c r="B358" s="43" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="C358" s="22" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="D358" s="16"/>
     </row>
@@ -21713,10 +21720,10 @@
         <v>176</v>
       </c>
       <c r="B359" s="45" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="C359" s="35" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="D359" s="16"/>
       <c r="E359" s="1"/>
@@ -21739,10 +21746,10 @@
         <v>176</v>
       </c>
       <c r="B360" s="45" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C360" s="35" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="D360" s="16"/>
     </row>
@@ -21751,10 +21758,10 @@
         <v>177</v>
       </c>
       <c r="B361" s="43" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="C361" s="29" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="D361" s="16"/>
     </row>
@@ -21763,10 +21770,10 @@
         <v>177</v>
       </c>
       <c r="B362" s="45" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="C362" s="37" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="D362" s="16"/>
     </row>
@@ -21775,10 +21782,10 @@
         <v>177</v>
       </c>
       <c r="B363" s="45" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C363" s="37" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="D363" s="16"/>
     </row>
@@ -21787,10 +21794,10 @@
         <v>177</v>
       </c>
       <c r="B364" s="45" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="C364" s="35" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="D364" s="16"/>
     </row>
@@ -21799,10 +21806,10 @@
         <v>178</v>
       </c>
       <c r="B365" s="45" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="C365" s="35" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="D365" s="16"/>
     </row>
@@ -21811,10 +21818,10 @@
         <v>178</v>
       </c>
       <c r="B366" s="43" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="C366" s="22" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="D366" s="16"/>
     </row>
@@ -21823,10 +21830,10 @@
         <v>178</v>
       </c>
       <c r="B367" s="45" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="C367" s="35" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="D367" s="16"/>
     </row>
@@ -21835,10 +21842,10 @@
         <v>179</v>
       </c>
       <c r="B368" s="45" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="C368" s="35" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="D368" s="16"/>
       <c r="E368" s="1"/>
@@ -21861,10 +21868,10 @@
         <v>179</v>
       </c>
       <c r="B369" s="43" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="C369" s="29" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="D369" s="16"/>
     </row>
@@ -21873,10 +21880,10 @@
         <v>179</v>
       </c>
       <c r="B370" s="45" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="C370" s="35" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="D370" s="16"/>
     </row>
@@ -21885,10 +21892,10 @@
         <v>179</v>
       </c>
       <c r="B371" s="43" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="C371" s="29" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="D371" s="16"/>
     </row>
@@ -21897,10 +21904,10 @@
         <v>179</v>
       </c>
       <c r="B372" s="45" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="C372" s="37" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="D372" s="16"/>
     </row>
@@ -21909,10 +21916,10 @@
         <v>179</v>
       </c>
       <c r="B373" s="45" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="C373" s="37" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="D373" s="16"/>
     </row>
@@ -21921,10 +21928,10 @@
         <v>180</v>
       </c>
       <c r="B374" s="45" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="C374" s="35" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="D374" s="16"/>
     </row>
@@ -21933,10 +21940,10 @@
         <v>180</v>
       </c>
       <c r="B375" s="45" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="C375" s="35" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="D375" s="16"/>
     </row>
@@ -21945,10 +21952,10 @@
         <v>180</v>
       </c>
       <c r="B376" s="45" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="C376" s="35" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="D376" s="16"/>
     </row>
@@ -21957,10 +21964,10 @@
         <v>180</v>
       </c>
       <c r="B377" s="45" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="C377" s="37" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="D377" s="16"/>
     </row>
@@ -21969,10 +21976,10 @@
         <v>181</v>
       </c>
       <c r="B378" s="43" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C378" s="22" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="D378" s="29"/>
       <c r="E378" s="29"/>
@@ -21995,10 +22002,10 @@
         <v>181</v>
       </c>
       <c r="B379" s="43" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="C379" s="22" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="D379" s="29"/>
       <c r="E379" s="29"/>
@@ -22021,10 +22028,10 @@
         <v>182</v>
       </c>
       <c r="B380" s="43" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="C380" s="22" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="D380" s="29"/>
       <c r="E380" s="29"/>
@@ -22047,10 +22054,10 @@
         <v>182</v>
       </c>
       <c r="B381" s="43" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="C381" s="22" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="D381" s="29"/>
       <c r="E381" s="29"/>
@@ -22073,10 +22080,10 @@
         <v>182</v>
       </c>
       <c r="B382" s="54" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="C382" s="55" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="383" s="5" customFormat="1" spans="1:18">
@@ -22084,10 +22091,10 @@
         <v>183</v>
       </c>
       <c r="B383" s="56" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="C383" s="57" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="D383" s="58"/>
       <c r="E383" s="58"/>
@@ -22110,10 +22117,10 @@
         <v>184</v>
       </c>
       <c r="B384" s="56" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C384" s="57" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="D384" s="58"/>
       <c r="E384" s="58"/>
@@ -22136,10 +22143,10 @@
         <v>187</v>
       </c>
       <c r="B385" s="56" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="C385" s="57" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="D385" s="58"/>
       <c r="E385" s="58"/>
@@ -22162,10 +22169,10 @@
         <v>188</v>
       </c>
       <c r="B386" s="56" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="C386" s="57" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="D386" s="58"/>
       <c r="E386" s="58"/>
@@ -22188,10 +22195,10 @@
         <v>189</v>
       </c>
       <c r="B387" s="56" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="C387" s="57" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="D387" s="58"/>
       <c r="E387" s="58"/>
@@ -22214,10 +22221,10 @@
         <v>190</v>
       </c>
       <c r="B388" s="56" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="C388" s="57" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="D388" s="58"/>
       <c r="E388" s="58"/>
@@ -22240,10 +22247,10 @@
         <v>190</v>
       </c>
       <c r="B389" s="56" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="C389" s="57" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="D389" s="58"/>
       <c r="E389" s="58"/>
@@ -22266,10 +22273,10 @@
         <v>190</v>
       </c>
       <c r="B390" s="54" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C390" s="55" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="D390" s="5"/>
       <c r="E390" s="5"/>
@@ -22292,10 +22299,10 @@
         <v>191</v>
       </c>
       <c r="B391" s="56" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="C391" s="57" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="D391" s="58"/>
       <c r="E391" s="58"/>
@@ -22318,10 +22325,10 @@
         <v>191</v>
       </c>
       <c r="B392" s="56" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="C392" s="57" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="D392" s="58"/>
       <c r="E392" s="58"/>
@@ -22344,10 +22351,10 @@
         <v>192</v>
       </c>
       <c r="B393" s="56" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="C393" s="57" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="D393" s="58"/>
       <c r="E393" s="58"/>
@@ -22370,10 +22377,10 @@
         <v>193</v>
       </c>
       <c r="B394" s="56" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="C394" s="57" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="D394" s="58"/>
       <c r="E394" s="58"/>
@@ -22396,10 +22403,10 @@
         <v>194</v>
       </c>
       <c r="B395" s="54" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="C395" s="55" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
     </row>
     <row r="396" s="5" customFormat="1" ht="115.2" spans="1:18">
@@ -22407,10 +22414,10 @@
         <v>195</v>
       </c>
       <c r="B396" s="56" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="C396" s="57" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="D396" s="58"/>
       <c r="E396" s="58"/>
@@ -22433,10 +22440,10 @@
         <v>196</v>
       </c>
       <c r="B397" s="56" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="C397" s="57" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="D397" s="58"/>
       <c r="E397" s="58"/>
@@ -22459,10 +22466,10 @@
         <v>197</v>
       </c>
       <c r="B398" s="56" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="C398" s="57" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="D398" s="58"/>
       <c r="E398" s="58"/>
@@ -22485,10 +22492,10 @@
         <v>198</v>
       </c>
       <c r="B399" s="56" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C399" s="57" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="D399" s="58"/>
       <c r="E399" s="58"/>
@@ -22511,10 +22518,10 @@
         <v>198</v>
       </c>
       <c r="B400" s="56" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="C400" s="57" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="D400" s="58"/>
       <c r="E400" s="58"/>
@@ -22537,10 +22544,10 @@
         <v>200</v>
       </c>
       <c r="B401" s="56" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="C401" s="57" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="D401" s="58"/>
       <c r="E401" s="58"/>
@@ -22563,10 +22570,10 @@
         <v>200</v>
       </c>
       <c r="B402" s="56" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="C402" s="57" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="D402" s="58"/>
       <c r="E402" s="58"/>
@@ -22589,10 +22596,10 @@
         <v>200</v>
       </c>
       <c r="B403" s="54" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="C403" s="55" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
     </row>
     <row r="404" s="5" customFormat="1" ht="100.8" spans="1:18">
@@ -22600,10 +22607,10 @@
         <v>202</v>
       </c>
       <c r="B404" s="59" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="C404" s="57" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="D404" s="58"/>
       <c r="E404" s="58"/>
@@ -22626,10 +22633,10 @@
         <v>203</v>
       </c>
       <c r="B405" s="56" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="C405" s="57" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="D405" s="58"/>
       <c r="E405" s="58"/>
@@ -22652,10 +22659,10 @@
         <v>203</v>
       </c>
       <c r="B406" s="54" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="C406" s="55" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="D406" s="5"/>
       <c r="E406" s="5"/>
@@ -22678,10 +22685,10 @@
         <v>204</v>
       </c>
       <c r="B407" s="56" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="C407" s="57" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="D407" s="58"/>
       <c r="E407" s="58"/>
@@ -22704,10 +22711,10 @@
         <v>205</v>
       </c>
       <c r="B408" s="56" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="C408" s="57" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="D408" s="58"/>
       <c r="E408" s="58"/>
@@ -22730,10 +22737,10 @@
         <v>206</v>
       </c>
       <c r="B409" s="56" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="C409" s="57" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="D409" s="58"/>
       <c r="E409" s="58"/>
@@ -22756,10 +22763,10 @@
         <v>206</v>
       </c>
       <c r="B410" s="56" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="C410" s="57" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="D410" s="58"/>
       <c r="E410" s="58"/>
@@ -22782,10 +22789,10 @@
         <v>207</v>
       </c>
       <c r="B411" s="56" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="C411" s="57" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="D411" s="58"/>
       <c r="E411" s="58"/>
@@ -22808,10 +22815,10 @@
         <v>208</v>
       </c>
       <c r="B412" s="56" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="C412" s="57" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="D412" s="58"/>
       <c r="E412" s="58"/>
@@ -22834,10 +22841,10 @@
         <v>209</v>
       </c>
       <c r="B413" s="56" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="C413" s="57" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="D413" s="58"/>
       <c r="E413" s="58"/>
@@ -22860,10 +22867,10 @@
         <v>210</v>
       </c>
       <c r="B414" s="56" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="C414" s="57" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="D414" s="58"/>
       <c r="E414" s="58"/>
@@ -22886,10 +22893,10 @@
         <v>210</v>
       </c>
       <c r="B415" s="56" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="C415" s="57" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="D415" s="58"/>
       <c r="E415" s="58"/>
@@ -22912,10 +22919,10 @@
         <v>212</v>
       </c>
       <c r="B416" s="54" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="C416" s="55" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
     </row>
     <row r="417" s="5" customFormat="1" ht="72" spans="1:18">
@@ -22923,10 +22930,10 @@
         <v>212</v>
       </c>
       <c r="B417" s="54" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="C417" s="55" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
     </row>
     <row r="418" s="5" customFormat="1" ht="72" spans="1:18">
@@ -22934,10 +22941,10 @@
         <v>213</v>
       </c>
       <c r="B418" s="56" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="C418" s="57" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="D418" s="58"/>
       <c r="E418" s="58"/>
@@ -22960,10 +22967,10 @@
         <v>213</v>
       </c>
       <c r="B419" s="56" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="C419" s="57" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="D419" s="58"/>
       <c r="E419" s="58"/>
@@ -22986,10 +22993,10 @@
         <v>214</v>
       </c>
       <c r="B420" s="54" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="C420" s="55" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
     </row>
     <row r="421" s="5" customFormat="1" ht="43.2" spans="1:18">
@@ -22997,10 +23004,10 @@
         <v>214</v>
       </c>
       <c r="B421" s="54" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="C421" s="55" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
     </row>
     <row r="422" s="5" customFormat="1" ht="72" spans="1:18">
@@ -23008,10 +23015,10 @@
         <v>214</v>
       </c>
       <c r="B422" s="54" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="C422" s="55" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
     </row>
     <row r="423" s="6" customFormat="1" ht="158.4" spans="1:18">
@@ -23019,10 +23026,10 @@
         <v>215</v>
       </c>
       <c r="B423" s="54" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="C423" s="55" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="D423" s="5"/>
       <c r="E423" s="5"/>
@@ -23045,10 +23052,10 @@
         <v>217</v>
       </c>
       <c r="B424" s="56" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="C424" s="57" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="D424" s="58"/>
       <c r="E424" s="58"/>
@@ -23071,10 +23078,10 @@
         <v>217</v>
       </c>
       <c r="B425" s="56" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="C425" s="57" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="D425" s="58"/>
       <c r="E425" s="58"/>
@@ -23097,10 +23104,10 @@
         <v>217</v>
       </c>
       <c r="B426" s="56" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="C426" s="57" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="D426" s="58"/>
       <c r="E426" s="58"/>
@@ -23123,10 +23130,10 @@
         <v>217</v>
       </c>
       <c r="B427" s="56" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="C427" s="57" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="D427" s="58"/>
       <c r="E427" s="58"/>
@@ -23149,10 +23156,10 @@
         <v>218</v>
       </c>
       <c r="B428" s="56" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="C428" s="57" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="D428" s="58"/>
       <c r="E428" s="58"/>
@@ -23175,10 +23182,10 @@
         <v>218</v>
       </c>
       <c r="B429" s="56" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="C429" s="57" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="D429" s="58"/>
       <c r="E429" s="58"/>
@@ -23201,10 +23208,10 @@
         <v>219</v>
       </c>
       <c r="B430" s="56" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="C430" s="57" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="D430" s="58"/>
       <c r="E430" s="58"/>
@@ -23227,10 +23234,10 @@
         <v>219</v>
       </c>
       <c r="B431" s="56" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="C431" s="57" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="D431" s="58"/>
       <c r="E431" s="58"/>
@@ -23253,10 +23260,10 @@
         <v>220</v>
       </c>
       <c r="B432" s="56" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="C432" s="57" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="D432" s="58"/>
       <c r="E432" s="58"/>
@@ -23279,10 +23286,10 @@
         <v>220</v>
       </c>
       <c r="B433" s="56" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="C433" s="57" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="D433" s="58"/>
       <c r="E433" s="58"/>
@@ -23305,10 +23312,10 @@
         <v>220</v>
       </c>
       <c r="B434" s="56" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="C434" s="57" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="D434" s="58"/>
       <c r="E434" s="58"/>
@@ -23331,10 +23338,10 @@
         <v>221</v>
       </c>
       <c r="B435" s="56" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="C435" s="57" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="D435" s="58"/>
       <c r="E435" s="58"/>
@@ -23357,10 +23364,10 @@
         <v>221</v>
       </c>
       <c r="B436" s="56" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="C436" s="57" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="D436" s="58"/>
       <c r="E436" s="58"/>
@@ -23383,10 +23390,10 @@
         <v>221</v>
       </c>
       <c r="B437" s="56" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="C437" s="57" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="D437" s="58"/>
       <c r="E437" s="58"/>
@@ -23409,10 +23416,10 @@
         <v>222</v>
       </c>
       <c r="B438" s="56" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="C438" s="57" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="D438" s="58"/>
       <c r="E438" s="58"/>
@@ -23435,10 +23442,10 @@
         <v>223</v>
       </c>
       <c r="B439" s="56" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="C439" s="57" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="D439" s="58"/>
       <c r="E439" s="58"/>
@@ -23461,10 +23468,10 @@
         <v>223</v>
       </c>
       <c r="B440" s="56" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="C440" s="57" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="D440" s="58"/>
       <c r="E440" s="58"/>
@@ -23487,10 +23494,10 @@
         <v>224</v>
       </c>
       <c r="B441" s="56" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="C441" s="57" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="D441" s="58"/>
       <c r="E441" s="58"/>
@@ -23513,10 +23520,10 @@
         <v>225</v>
       </c>
       <c r="B442" s="56" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="C442" s="57" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="D442" s="58"/>
       <c r="E442" s="58"/>
@@ -23539,10 +23546,10 @@
         <v>225</v>
       </c>
       <c r="B443" s="56" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="C443" s="57" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="D443" s="58"/>
       <c r="E443" s="58"/>
@@ -23565,10 +23572,10 @@
         <v>225</v>
       </c>
       <c r="B444" s="56" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="C444" s="57" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="D444" s="58"/>
       <c r="E444" s="58"/>
@@ -23591,10 +23598,10 @@
         <v>225</v>
       </c>
       <c r="B445" s="56" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="C445" s="57" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="D445" s="58"/>
       <c r="E445" s="58"/>
@@ -23617,10 +23624,10 @@
         <v>226</v>
       </c>
       <c r="B446" s="56" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="C446" s="57" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="D446" s="58"/>
       <c r="E446" s="58"/>
@@ -23643,10 +23650,10 @@
         <v>226</v>
       </c>
       <c r="B447" s="56" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="C447" s="57" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="D447" s="58"/>
       <c r="E447" s="58"/>
@@ -23669,10 +23676,10 @@
         <v>226</v>
       </c>
       <c r="B448" s="56" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="C448" s="57" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="D448" s="58"/>
       <c r="E448" s="58"/>
@@ -23695,10 +23702,10 @@
         <v>227</v>
       </c>
       <c r="B449" s="56" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="C449" s="57" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="D449" s="58"/>
       <c r="E449" s="58"/>
@@ -23721,10 +23728,10 @@
         <v>227</v>
       </c>
       <c r="B450" s="54" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="C450" s="55" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
     </row>
     <row r="451" s="5" customFormat="1" ht="57.6" spans="1:18">
@@ -23732,10 +23739,10 @@
         <v>228</v>
       </c>
       <c r="B451" s="56" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="C451" s="57" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="D451" s="58"/>
       <c r="E451" s="58"/>
@@ -23758,10 +23765,10 @@
         <v>228</v>
       </c>
       <c r="B452" s="54" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="C452" s="55" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
     </row>
     <row r="453" s="5" customFormat="1" ht="43.2" spans="1:18">
@@ -23769,10 +23776,10 @@
         <v>229</v>
       </c>
       <c r="B453" s="56" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="C453" s="57" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="D453" s="58"/>
       <c r="E453" s="58"/>
@@ -23795,10 +23802,10 @@
         <v>230</v>
       </c>
       <c r="B454" s="56" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="C454" s="57" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="D454" s="58"/>
       <c r="E454" s="58"/>
@@ -23821,10 +23828,10 @@
         <v>230</v>
       </c>
       <c r="B455" s="56" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="C455" s="57" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="D455" s="58"/>
       <c r="E455" s="58"/>
@@ -23847,10 +23854,10 @@
         <v>230</v>
       </c>
       <c r="B456" s="54" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="C456" s="55" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
     </row>
     <row r="457" s="5" customFormat="1" spans="1:18">
@@ -23858,10 +23865,10 @@
         <v>230</v>
       </c>
       <c r="B457" s="54" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="C457" s="55" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
     </row>
     <row r="458" s="5" customFormat="1" spans="1:18">
@@ -23869,10 +23876,10 @@
         <v>231</v>
       </c>
       <c r="B458" s="56" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="C458" s="57" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="D458" s="58"/>
       <c r="E458" s="58"/>
@@ -23895,10 +23902,10 @@
         <v>231</v>
       </c>
       <c r="B459" s="56" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="C459" s="57" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="D459" s="58"/>
       <c r="E459" s="58"/>
@@ -23921,10 +23928,10 @@
         <v>231</v>
       </c>
       <c r="B460" s="56" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="C460" s="57" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="D460" s="58"/>
       <c r="E460" s="58"/>
@@ -23947,10 +23954,10 @@
         <v>233</v>
       </c>
       <c r="B461" s="56" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="C461" s="57" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="D461" s="58"/>
       <c r="E461" s="58"/>
@@ -23973,10 +23980,10 @@
         <v>233</v>
       </c>
       <c r="B462" s="56" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="C462" s="57" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="D462" s="58"/>
       <c r="E462" s="58"/>
@@ -23999,10 +24006,10 @@
         <v>234</v>
       </c>
       <c r="B463" s="56" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="C463" s="57" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="D463" s="58"/>
       <c r="E463" s="58"/>
@@ -24025,10 +24032,10 @@
         <v>234</v>
       </c>
       <c r="B464" s="54" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="C464" s="55" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
     </row>
     <row r="465" s="5" customFormat="1" ht="43.2" spans="1:18">
@@ -24036,10 +24043,10 @@
         <v>234</v>
       </c>
       <c r="B465" s="54" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="C465" s="55" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="466" s="5" customFormat="1" spans="1:18">
@@ -24047,10 +24054,10 @@
         <v>235</v>
       </c>
       <c r="B466" s="56" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="C466" s="58" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="D466" s="58"/>
       <c r="E466" s="58"/>
@@ -24073,10 +24080,10 @@
         <v>235</v>
       </c>
       <c r="B467" s="56" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="C467" s="58" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="D467" s="58"/>
       <c r="E467" s="58"/>
@@ -24099,10 +24106,10 @@
         <v>236</v>
       </c>
       <c r="B468" s="56" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="C468" s="57" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="D468" s="58"/>
       <c r="E468" s="58"/>
@@ -24125,10 +24132,10 @@
         <v>237</v>
       </c>
       <c r="B469" s="56" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="C469" s="57" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="D469" s="58"/>
       <c r="E469" s="58"/>
@@ -24151,10 +24158,10 @@
         <v>237</v>
       </c>
       <c r="B470" s="54" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="C470" s="5" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="D470" s="5"/>
       <c r="E470" s="5"/>
@@ -24177,10 +24184,10 @@
         <v>238</v>
       </c>
       <c r="B471" s="56" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="C471" s="58" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="D471" s="58"/>
       <c r="E471" s="58"/>
@@ -24203,10 +24210,10 @@
         <v>238</v>
       </c>
       <c r="B472" s="56" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="C472" s="58" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="D472" s="58"/>
       <c r="E472" s="58"/>
@@ -24229,10 +24236,10 @@
         <v>238</v>
       </c>
       <c r="B473" s="54" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="C473" s="5" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
     </row>
     <row r="474" s="5" customFormat="1" ht="43.2" spans="1:18">
@@ -24240,10 +24247,10 @@
         <v>239</v>
       </c>
       <c r="B474" s="56" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="C474" s="57" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="D474" s="58"/>
       <c r="E474" s="58"/>
@@ -24266,10 +24273,10 @@
         <v>240</v>
       </c>
       <c r="B475" s="56" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="C475" s="58" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="D475" s="58"/>
       <c r="E475" s="58"/>
@@ -24292,10 +24299,10 @@
         <v>241</v>
       </c>
       <c r="B476" s="56" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="C476" s="57" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="D476" s="58"/>
       <c r="E476" s="58"/>
@@ -24318,10 +24325,10 @@
         <v>241</v>
       </c>
       <c r="B477" s="56" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="C477" s="58" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="D477" s="58"/>
       <c r="E477" s="58"/>
@@ -24344,10 +24351,10 @@
         <v>241</v>
       </c>
       <c r="B478" s="56" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="C478" s="58" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="D478" s="58"/>
       <c r="E478" s="58"/>
@@ -24370,10 +24377,10 @@
         <v>241</v>
       </c>
       <c r="B479" s="56" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="C479" s="58" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="D479" s="58"/>
       <c r="E479" s="58"/>
@@ -24396,10 +24403,10 @@
         <v>241</v>
       </c>
       <c r="B480" s="56" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="C480" s="58" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="D480" s="58"/>
       <c r="E480" s="58"/>
@@ -24422,10 +24429,10 @@
         <v>242</v>
       </c>
       <c r="B481" s="56" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="C481" s="58" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="D481" s="58"/>
       <c r="E481" s="58"/>
@@ -24448,10 +24455,10 @@
         <v>242</v>
       </c>
       <c r="B482" s="54" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="C482" s="5" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="483" s="5" customFormat="1" ht="57.6" spans="1:18">
@@ -24459,10 +24466,10 @@
         <v>243</v>
       </c>
       <c r="B483" s="56" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="C483" s="57" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="D483" s="58"/>
       <c r="E483" s="58"/>
@@ -24485,10 +24492,10 @@
         <v>243</v>
       </c>
       <c r="B484" s="56" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="C484" s="57" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="D484" s="58"/>
       <c r="E484" s="58"/>
@@ -24511,10 +24518,10 @@
         <v>244</v>
       </c>
       <c r="B485" s="60" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="C485" s="57" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="D485" s="58"/>
       <c r="E485" s="58"/>
@@ -24537,10 +24544,10 @@
         <v>244</v>
       </c>
       <c r="B486" s="43" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="C486" s="29" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D486" s="58"/>
       <c r="E486" s="58"/>
@@ -24563,10 +24570,10 @@
         <v>244</v>
       </c>
       <c r="B487" s="54" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="C487" s="5" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="488" s="5" customFormat="1" ht="86.4" spans="1:18">
@@ -24574,10 +24581,10 @@
         <v>245</v>
       </c>
       <c r="B488" s="56" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="C488" s="57" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="D488" s="58"/>
       <c r="E488" s="58"/>
@@ -24600,10 +24607,10 @@
         <v>245</v>
       </c>
       <c r="B489" s="56" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="C489" s="58" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="D489" s="58"/>
       <c r="E489" s="58"/>
@@ -24626,10 +24633,10 @@
         <v>246</v>
       </c>
       <c r="B490" s="56" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="C490" s="58" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="D490" s="58"/>
       <c r="E490" s="58"/>
@@ -24652,10 +24659,10 @@
         <v>246</v>
       </c>
       <c r="B491" s="54" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="C491" s="5" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="492" s="5" customFormat="1" ht="28.8" spans="1:18">
@@ -24663,10 +24670,10 @@
         <v>246</v>
       </c>
       <c r="B492" s="54" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="C492" s="55" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="493" s="5" customFormat="1" ht="28.8" spans="1:18">
@@ -24674,10 +24681,10 @@
         <v>246</v>
       </c>
       <c r="B493" s="54" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="C493" s="55" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="494" s="5" customFormat="1" ht="100.8" spans="1:18">
@@ -24685,10 +24692,10 @@
         <v>247</v>
       </c>
       <c r="B494" s="56" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="C494" s="57" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="D494" s="58"/>
       <c r="E494" s="58"/>
@@ -24711,10 +24718,10 @@
         <v>247</v>
       </c>
       <c r="B495" s="56" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="C495" s="58" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="D495" s="58"/>
       <c r="E495" s="58"/>
@@ -24737,10 +24744,10 @@
         <v>249</v>
       </c>
       <c r="B496" s="56" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="C496" s="58" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="D496" s="58"/>
       <c r="E496" s="58"/>
@@ -24763,10 +24770,10 @@
         <v>249</v>
       </c>
       <c r="B497" s="56" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="C497" s="57" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="D497" s="58"/>
       <c r="E497" s="58"/>
@@ -24789,10 +24796,10 @@
         <v>249</v>
       </c>
       <c r="B498" s="54" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="C498" s="5" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="D498" s="5"/>
       <c r="E498" s="5"/>
@@ -24815,10 +24822,10 @@
         <v>250</v>
       </c>
       <c r="B499" s="56" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="C499" s="57" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="D499" s="58"/>
       <c r="E499" s="58"/>
@@ -24841,10 +24848,10 @@
         <v>250</v>
       </c>
       <c r="B500" s="56" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C500" s="57" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="D500" s="58"/>
       <c r="E500" s="58"/>
@@ -24867,10 +24874,10 @@
         <v>250</v>
       </c>
       <c r="B501" s="56" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="C501" s="58" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="D501" s="58"/>
       <c r="E501" s="58"/>
@@ -24893,10 +24900,10 @@
         <v>251</v>
       </c>
       <c r="B502" s="56" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="C502" s="57" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="D502" s="58"/>
       <c r="E502" s="58"/>
@@ -24919,10 +24926,10 @@
         <v>252</v>
       </c>
       <c r="B503" s="56" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="C503" s="58" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="D503" s="58"/>
       <c r="E503" s="58"/>
@@ -24945,10 +24952,10 @@
         <v>252</v>
       </c>
       <c r="B504" s="56" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="C504" s="58" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="D504" s="58"/>
       <c r="E504" s="58"/>
@@ -24971,10 +24978,10 @@
         <v>254</v>
       </c>
       <c r="B505" s="56" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="C505" s="57" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="D505" s="58"/>
       <c r="E505" s="58"/>
@@ -24997,10 +25004,10 @@
         <v>255</v>
       </c>
       <c r="B506" s="56" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="C506" s="57" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="D506" s="58"/>
       <c r="E506" s="58"/>
@@ -25023,10 +25030,10 @@
         <v>255</v>
       </c>
       <c r="B507" s="54" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="C507" s="55" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="508" s="5" customFormat="1" spans="1:18">
@@ -25034,10 +25041,10 @@
         <v>255</v>
       </c>
       <c r="B508" s="54" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="C508" s="5" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="509" s="5" customFormat="1" spans="1:18">
@@ -25045,10 +25052,10 @@
         <v>256</v>
       </c>
       <c r="B509" s="56" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="C509" s="58" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="D509" s="58"/>
       <c r="E509" s="58"/>
@@ -25071,10 +25078,10 @@
         <v>256</v>
       </c>
       <c r="B510" s="56" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="C510" s="58" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="D510" s="58"/>
       <c r="E510" s="58"/>
@@ -25097,10 +25104,10 @@
         <v>256</v>
       </c>
       <c r="B511" s="54" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="C511" s="5" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="512" s="5" customFormat="1" ht="57.6" spans="1:18">
@@ -25108,10 +25115,10 @@
         <v>257</v>
       </c>
       <c r="B512" s="56" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="C512" s="57" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="D512" s="58"/>
       <c r="E512" s="58"/>
@@ -25134,10 +25141,10 @@
         <v>257</v>
       </c>
       <c r="B513" s="54" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="C513" s="61" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="514" s="5" customFormat="1" spans="1:18">
@@ -25145,10 +25152,10 @@
         <v>258</v>
       </c>
       <c r="B514" s="56" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="C514" s="58" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="D514" s="58"/>
       <c r="E514" s="58"/>
@@ -25171,10 +25178,10 @@
         <v>258</v>
       </c>
       <c r="B515" s="56" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="C515" s="58" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="D515" s="58"/>
       <c r="E515" s="58"/>
@@ -25197,10 +25204,10 @@
         <v>258</v>
       </c>
       <c r="B516" s="56" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="C516" s="57" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="D516" s="58"/>
       <c r="E516" s="58"/>
@@ -25223,10 +25230,10 @@
         <v>259</v>
       </c>
       <c r="B517" s="56" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="C517" s="58" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="D517" s="58"/>
       <c r="E517" s="58"/>
@@ -25252,7 +25259,7 @@
         <v>1001</v>
       </c>
       <c r="C518" s="58" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="D518" s="58"/>
       <c r="E518" s="58"/>
@@ -25275,10 +25282,10 @@
         <v>260</v>
       </c>
       <c r="B519" s="56" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="C519" s="58" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="D519" s="58"/>
       <c r="E519" s="58"/>
@@ -25304,7 +25311,7 @@
         <v>1000</v>
       </c>
       <c r="C520" s="58" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="D520" s="58"/>
       <c r="E520" s="58"/>
@@ -25327,10 +25334,10 @@
         <v>260</v>
       </c>
       <c r="B521" s="54" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="C521" s="5" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="D521" s="5"/>
       <c r="E521" s="5"/>
@@ -25353,10 +25360,10 @@
         <v>263</v>
       </c>
       <c r="B522" s="56" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="C522" s="58" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="D522" s="58"/>
       <c r="E522" s="58"/>
@@ -25379,10 +25386,10 @@
         <v>263</v>
       </c>
       <c r="B523" s="56" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="C523" s="57" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="D523" s="58"/>
       <c r="E523" s="58"/>
@@ -25405,21 +25412,21 @@
         <v>263</v>
       </c>
       <c r="B524" s="54" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="C524" s="5" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="525" s="5" customFormat="1" ht="57.6" spans="1:18">
       <c r="A525" s="62" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="B525" s="63" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="C525" s="64" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="D525" s="65"/>
       <c r="E525" s="66"/>
@@ -25439,13 +25446,13 @@
     </row>
     <row r="526" s="5" customFormat="1" ht="28.8" spans="1:18">
       <c r="A526" s="62" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="B526" s="63" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="C526" s="64" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="D526" s="65"/>
       <c r="E526" s="66"/>
@@ -25465,13 +25472,13 @@
     </row>
     <row r="527" s="5" customFormat="1" ht="158.4" spans="1:18">
       <c r="A527" s="62" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="B527" s="63" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="C527" s="64" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="D527" s="65"/>
       <c r="E527" s="66"/>
@@ -25491,13 +25498,13 @@
     </row>
     <row r="528" s="5" customFormat="1" ht="43.2" spans="1:18">
       <c r="A528" s="62" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="B528" s="63" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="C528" s="57" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="D528" s="65"/>
       <c r="E528" s="66"/>
@@ -25517,13 +25524,13 @@
     </row>
     <row r="529" s="6" customFormat="1" ht="100.8" spans="1:18">
       <c r="A529" s="62" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="B529" s="63" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="C529" s="67" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="D529" s="65"/>
       <c r="E529" s="66"/>
@@ -25543,13 +25550,13 @@
     </row>
     <row r="530" s="6" customFormat="1" ht="409.5" spans="1:18">
       <c r="A530" s="62" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="B530" s="63" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="C530" s="64" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="D530" s="65"/>
       <c r="E530" s="66"/>
